--- a/Outputs/Scenarios/PtX_demand_BE_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_BE_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001354470379864105</v>
       </c>
       <c r="K16" t="n">
-        <v>0.008466705400423441</v>
+        <v>0.009498761543690178</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.001872358979105462</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01693341080084688</v>
+        <v>0.0149788718328437</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
         <v>1.951562544001469e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00282223513347448</v>
+        <v>0.001872358979105462</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.002005128495497259</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0455901374767656</v>
+        <v>0.05114738545340098</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.0100819739469151</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0911802749535312</v>
+        <v>0.08065579157532081</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0001055330787103821</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0151967124922552</v>
+        <v>0.0100819739469151</v>
       </c>
     </row>
     <row r="43">
